--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>415</v>
+        <v>184</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>410</v>
+        <v>175</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D2">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="H3">
         <v>426</v>
